--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:01</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:47</t>
+    <t xml:space="preserve">2026-10-05 10:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -690,7 +690,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>746254.12</v>
+        <v>746254.13</v>
       </c>
     </row>
     <row r="10">
@@ -758,7 +758,7 @@
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>701333.62</v>
+        <v>701333.63</v>
       </c>
     </row>
     <row r="14">
@@ -826,7 +826,7 @@
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>665883.62</v>
+        <v>665883.63</v>
       </c>
     </row>
     <row r="18">
@@ -928,7 +928,7 @@
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>623640.12</v>
+        <v>623640.13</v>
       </c>
     </row>
     <row r="24">
